--- a/data/trans_bre/P16A12-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,38</t>
+          <t>-3,51; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 4,14</t>
+          <t>-4,46; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,52</t>
+          <t>-6,37; 0,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,82</t>
+          <t>-6,48; 1,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 127,48</t>
+          <t>-59,57; 128,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 93,61</t>
+          <t>-53,77; 93,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,43; 19,97</t>
+          <t>-76,37; 17,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 12,38</t>
+          <t>-50,84; 18,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,79</t>
+          <t>-0,51; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,73</t>
+          <t>0,51; 7,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,44</t>
+          <t>0,02; 7,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,91</t>
+          <t>-2,13; 4,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 138,53</t>
+          <t>-7,74; 150,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 149,75</t>
+          <t>3,71; 145,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 135,56</t>
+          <t>0,28; 142,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 81,71</t>
+          <t>-25,42; 89,23</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 6,42</t>
+          <t>-1,14; 5,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,91</t>
+          <t>-4,84; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,65</t>
+          <t>-1,39; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,59</t>
+          <t>-5,04; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 208,65</t>
+          <t>-18,37; 178,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 62,69</t>
+          <t>-38,51; 62,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 196,7</t>
+          <t>-25,99; 187,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 28,33</t>
+          <t>-37,82; 28,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,53</t>
+          <t>-3,31; 2,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,8</t>
+          <t>-1,59; 5,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -1,63</t>
+          <t>-9,7; -1,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,4</t>
+          <t>-7,04; 0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,39; 71,02</t>
+          <t>-51,96; 72,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 130,99</t>
+          <t>-20,44; 135,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,94; -15,57</t>
+          <t>-66,68; -12,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 8,4</t>
+          <t>-64,67; 1,52</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 9,59</t>
+          <t>-0,65; 9,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,16</t>
+          <t>-3,09; 8,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 8,63</t>
+          <t>-1,47; 8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,23</t>
+          <t>-2,87; 6,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 351,58</t>
+          <t>-16,84; 300,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 157,74</t>
+          <t>-26,27; 146,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 212,87</t>
+          <t>-23,75; 190,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 81,84</t>
+          <t>-21,72; 84,54</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 1,17</t>
+          <t>-6,1; 1,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 8,27</t>
+          <t>-0,49; 8,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,82</t>
+          <t>-3,88; 4,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,25</t>
+          <t>-7,9; 0,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 45,94</t>
+          <t>-76,86; 45,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 162,95</t>
+          <t>-8,0; 185,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 104,65</t>
+          <t>-46,56; 101,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 2,71</t>
+          <t>-47,12; 3,57</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,2</t>
+          <t>-2,75; 2,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,04</t>
+          <t>-2,97; 2,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,57</t>
+          <t>-6,4; 0,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -1,52</t>
+          <t>-7,76; -1,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 39,34</t>
+          <t>-35,38; 50,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 46,76</t>
+          <t>-30,72; 44,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 7,84</t>
+          <t>-51,04; 4,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,09; -21,88</t>
+          <t>-77,4; -21,25</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,29</t>
+          <t>-2,64; 2,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,7</t>
+          <t>-2,94; 1,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,73</t>
+          <t>-2,93; 2,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,25</t>
+          <t>-1,51; 4,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 46,93</t>
+          <t>-36,81; 47,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 37,37</t>
+          <t>-40,45; 35,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 36,58</t>
+          <t>-29,37; 33,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 143,77</t>
+          <t>-22,45; 191,02</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,62</t>
+          <t>-0,7; 1,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,14; 2,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,79</t>
+          <t>-1,85; 0,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,55</t>
+          <t>-2,71; 0,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 31,06</t>
+          <t>-11,46; 32,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 36,34</t>
+          <t>-1,72; 38,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 10,53</t>
+          <t>-20,08; 11,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 5,28</t>
+          <t>-30,4; 9,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A12-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-25,48%</t>
+          <t>-23,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,3</t>
+          <t>-3,62; 3,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 3,88</t>
+          <t>-4,21; 4,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 0,59</t>
+          <t>-6,62; 0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,34</t>
+          <t>-5,9; 1,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,57; 128,26</t>
+          <t>-60,09; 125,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,77; 93,99</t>
+          <t>-48,72; 106,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,37; 17,8</t>
+          <t>-75,31; 17,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 18,95</t>
+          <t>-48,27; 14,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,74</t>
+          <t>-0,89; 5,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,9</t>
+          <t>0,4; 7,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,11</t>
+          <t>-0,22; 7,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,04</t>
+          <t>-1,95; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 150,75</t>
+          <t>-12,75; 150,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 145,37</t>
+          <t>2,78; 150,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 142,16</t>
+          <t>-2,58; 141,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 89,23</t>
+          <t>-23,61; 83,28</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-8,94%</t>
+          <t>-9,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,97</t>
+          <t>-0,71; 6,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,87</t>
+          <t>-4,91; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,48</t>
+          <t>-1,18; 5,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,51</t>
+          <t>-4,51; 2,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 178,77</t>
+          <t>-12,73; 202,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 62,97</t>
+          <t>-37,54; 66,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 187,0</t>
+          <t>-25,46; 211,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 28,28</t>
+          <t>-34,14; 31,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,88%</t>
+          <t>-24,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,57</t>
+          <t>-3,52; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,79</t>
+          <t>-1,59; 5,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -1,15</t>
+          <t>-10,38; -1,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 0,11</t>
+          <t>-5,61; 1,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 72,28</t>
+          <t>-50,24; 88,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 135,27</t>
+          <t>-22,11; 137,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,68; -12,63</t>
+          <t>-68,34; -11,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 1,52</t>
+          <t>-49,85; 21,32</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,74</t>
+          <t>-0,62; 9,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 8,79</t>
+          <t>-2,68; 9,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 8,15</t>
+          <t>-1,34; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,56</t>
+          <t>-2,2; 6,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 300,5</t>
+          <t>-10,66; 327,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 146,36</t>
+          <t>-24,54; 152,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 190,92</t>
+          <t>-19,26; 205,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 84,54</t>
+          <t>-18,31; 87,84</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-3,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-26,53%</t>
+          <t>-26,69%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,19</t>
+          <t>-5,95; 1,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,77</t>
+          <t>-1,12; 8,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,58</t>
+          <t>-4,09; 4,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 0,39</t>
+          <t>-7,99; 0,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 45,75</t>
+          <t>-77,31; 40,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 185,04</t>
+          <t>-15,45; 185,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 101,5</t>
+          <t>-51,0; 96,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 3,57</t>
+          <t>-47,39; 3,85</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-47,97%</t>
+          <t>-34,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,53</t>
+          <t>-2,81; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,94</t>
+          <t>-3,0; 3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,36</t>
+          <t>-6,6; 0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,47</t>
+          <t>-5,58; -0,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 50,48</t>
+          <t>-35,07; 44,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 44,5</t>
+          <t>-30,71; 47,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 4,39</t>
+          <t>-51,76; 1,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,4; -21,25</t>
+          <t>-53,62; -6,43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>-7,57%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,09</t>
+          <t>-2,64; 2,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,78</t>
+          <t>-3,37; 1,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,65</t>
+          <t>-2,8; 2,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,74</t>
+          <t>-2,59; 1,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 47,66</t>
+          <t>-37,7; 44,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 35,69</t>
+          <t>-44,34; 34,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 33,73</t>
+          <t>-28,11; 35,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 191,02</t>
+          <t>-33,48; 28,58</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-14,96%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,67</t>
+          <t>-0,69; 1,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,54</t>
+          <t>-0,22; 2,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,9</t>
+          <t>-1,75; 1,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,68</t>
+          <t>-2,34; -0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 32,72</t>
+          <t>-11,07; 29,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 38,14</t>
+          <t>-2,67; 36,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 11,79</t>
+          <t>-19,65; 14,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,49</t>
+          <t>-24,5; -2,26</t>
         </is>
       </c>
     </row>
